--- a/inferences/jesuita-entrada-Coimbra-extra_info.xlsx
+++ b/inferences/jesuita-entrada-Coimbra-extra_info.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>jesuita-entrada.original.comment</t>
+          <t>jesuita-entrada.comment</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 Domingues &amp; O Neil, IV: 2645. MMHM:p.226', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date', 'comment': 'ou 15600325 ou Coimbra, 25-03-1560 MMHM'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
+          <t>{'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 Domingues &amp; O Neil, IV: 2645. MMHM:p.226', 'original': '?'}, 'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date', 'comment': 'ou 15600325 ou Coimbra, 25-03-1560 MMHM'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -530,12 +530,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Está no "Catálogo delos Padres y Hermanos dela Provincia de Portugal a 12 de Enero de 1579",Lus. 39 p.3v, nos estudantes de Filosofia do segundo curso</t>
+          <t>@wikidata:Q45412 Está no "Catálogo delos Padres y Hermanos dela Provincia de Portugal a 12 de Enero de 1579",Lus. 39 p.3v, nos estudantes de Filosofia do segundo curso</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': 'Está no "Catálogo delos Padres y Hermanos dela Provincia de Portugal a 12 de Enero de 1579",Lus. 39 p.3v, nos estudantes de Filosofia do segundo curso', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
+          <t>{'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 Está no "Catálogo delos Padres y Hermanos dela Provincia de Portugal a 12 de Enero de 1579",Lus. 39 p.3v, nos estudantes de Filosofia do segundo curso', 'original': '?'}, 'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 Schutte, Monumenta historica japoniae I.,p.1180', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
+          <t>{'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 Schutte, Monumenta historica japoniae I.,p.1180', 'original': '?'}, 'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -604,12 +604,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>"Catálogo delos Padres y Hermanos dela Provincia de Portugal a 12 de Enero de 1579" Lus. 39, 3v, estudante de filosofia, 1ºcurso</t>
+          <t>@wikidata:Q45412 "Catálogo delos Padres y Hermanos dela Provincia de Portugal a 12 de Enero de 1579" Lus. 39, 3v, estudante de filosofia, 1ºcurso</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '"Catálogo delos Padres y Hermanos dela Provincia de Portugal a 12 de Enero de 1579" Lus. 39, 3v, estudante de filosofia, 1ºcurso', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
+          <t>{'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 "Catálogo delos Padres y Hermanos dela Provincia de Portugal a 12 de Enero de 1579" Lus. 39, 3v, estudante de filosofia, 1ºcurso', 'original': '?'}, 'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 Em Coimbra no ano de 1582 segundo a Carta Annua de 1623 BA', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'obs': {'kleio_element_name': 'obs', 'kleio_element_class': 'obs', 'entity_attr_name': 'obs', 'entity_column_class': 'obs'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
+          <t>{'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 Em Coimbra no ano de 1582 segundo a Carta Annua de 1623 BA', 'original': '?'}, 'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'obs': {'kleio_element_name': 'obs', 'kleio_element_class': 'obs', 'entity_attr_name': 'obs', 'entity_column_class': 'obs'}}</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 MMHM:p.94 (ARSI Japsin 35 13)', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
+          <t>{'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 MMHM:p.94 (ARSI Japsin 35 13)', 'original': '?'}, 'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 Segundo Dominguez &amp; O Neil, V.III,p.2961. Franco Imagem...Coimbra,II,4,c.36,p.575', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
+          <t>{'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 Segundo Dominguez &amp; O Neil, V.III,p.2961. Franco Imagem...Coimbra,II,4,c.36,p.575', 'original': '?'}, 'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -752,12 +752,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>([Schütte, 1975, p. 1321] Sebastião Vieira, nasc Castro de Aire, Lamego, E. Coimbra 3-2-1591</t>
+          <t>@wikidata:Q45412([Schütte, 1975, p. 1321] Sebastião Vieira, nasc Castro de Aire, Lamego, E. Coimbra 3-2-1591</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '([Schütte, 1975, p. 1321] Sebastião Vieira, nasc Castro de Aire, Lamego, E. Coimbra 3-2-1591', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
+          <t>{'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412([Schütte, 1975, p. 1321] Sebastião Vieira, nasc Castro de Aire, Lamego, E. Coimbra 3-2-1591', 'original': '?'}, 'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 Segungo Dominguez, J. M., &amp; O’Neill, C. (2001) II, 1113', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
+          <t>{'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 Segungo Dominguez, J. M., &amp; O’Neill, C. (2001) II, 1113', 'original': '?'}, 'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 Dehergne não especifica local, Brockey estudos Filosofia e Teologia em Coimbra', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
+          <t>{'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 Dehergne não especifica local, Brockey estudos Filosofia e Teologia em Coimbra', 'original': '?'}, 'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 (Franco, 1719, t.II, p. 612)', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date', 'comment': 'ou 16090502 reentrou em 1611 não se sabe onde'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
+          <t>{'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 (Franco, 1719, t.II, p. 612)', 'original': '?'}, 'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date', 'comment': 'ou 16090502 reentrou em 1611 não se sabe onde'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '[Adicionado a partir de Franco, Imagem...Coimbra, II, 522] @wikidata:Q45412', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date', 'comment': 'MMHM:p.8'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
+          <t>{'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '[Adicionado a partir de Franco, Imagem...Coimbra, II, 522] @wikidata:Q45412', 'original': '?'}, 'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date', 'comment': 'MMHM:p.8'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 """Franco, Imagem...Coimbra, v.2 p.616; Barbosa Machado, v.3"""', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
+          <t>{'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 """Franco, Imagem...Coimbra, v.2 p.616; Barbosa Machado, v.3"""', 'original': '?'}, 'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -979,7 +979,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': "@wikidata:Q45412 MMHM:p.205 (Sebastian da Maia, da Maya, d'Amaya)", 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
+          <t>{'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': "@wikidata:Q45412 MMHM:p.205 (Sebastian da Maia, da Maya, d'Amaya)", 'original': '?'}, 'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 Segundo Louis Buglio 1688', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
+          <t>{'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 Segundo Louis Buglio 1688', 'original': '?'}, 'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
@@ -1053,19 +1053,19 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': "@wikidata:Q45412 MMHM:p.203 (Matias d'Amaia), Schutte, Monumenta historica japoniae I.1234", 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
+          <t>{'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': "@wikidata:Q45412 MMHM:p.203 (Matias d'Amaia), Schutte, Monumenta historica japoniae I.1234", 'original': '?'}, 'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>deh-adriano-pestana</t>
+          <t>deh-goncalo-da-fonseca</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Adriano Pestana</t>
+          <t>Gonçalo da Fonseca</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>16350000</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1085,49 +1085,86 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>@wikidata:Q45412 Ver Brockey, p.230 cit. Carta de A.P. a Viteleschi, de Coimbra, 26 Agosto 1640</t>
+          <t>@wikidata:Q45412 Segundo Schütte, p.1174</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 Ver Brockey, p.230 cit. Carta de A.P. a Viteleschi, de Coimbra, 26 Agosto 1640', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
+          <t>{'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 Segundo Schütte, p.1174', 'original': '?'}, 'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
+          <t>deh-adriano-pestana</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Adriano Pestana</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>16350000</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>@wikidata:Q45412 Ver Brockey, p.230 cit. Carta de A.P. a Viteleschi, de Coimbra, 26 Agosto 1640</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>{'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 Ver Brockey, p.230 cit. Carta de A.P. a Viteleschi, de Coimbra, 26 Agosto 1640', 'original': '?'}, 'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
           <t>deh-andre-ferrao</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>André Ferrão</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Coimbra</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>1640</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>@wikidata:Q45412 Brockey, cap.6 n.95</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>{'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 Brockey, cap.6 n.95', 'original': '?'}, 'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'obs': {'kleio_element_name': 'obs', 'kleio_element_class': 'obs', 'entity_attr_name': 'obs', 'entity_column_class': 'obs'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}}</t>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>{'id': {'kleio_element_name': 'id', 'kleio_element_class': 'id', 'entity_attr_name': 'id', 'entity_column_class': 'id'}, 'the_value': {'kleio_element_name': 'valor', 'kleio_element_class': 'value', 'entity_attr_name': 'value', 'entity_column_class': 'value', 'comment': '@wikidata:Q45412 Brockey, cap.6 n.95', 'original': '?'}, 'the_type': {'kleio_element_name': 'tipo', 'kleio_element_class': 'type', 'entity_attr_name': 'type', 'entity_column_class': 'type'}, 'the_date': {'kleio_element_name': 'date', 'kleio_element_class': 'date', 'entity_attr_name': 'date', 'entity_column_class': 'date'}, 'entity': {'kleio_element_name': 'entity', 'kleio_element_class': 'entity', 'entity_attr_name': 'entity', 'entity_column_class': 'entity'}, 'class': {'kleio_element_name': 'class', 'kleio_element_class': 'class', 'entity_attr_name': 'class', 'entity_column_class': 'class'}, 'obs': {'kleio_element_name': 'obs', 'kleio_element_class': 'obs', 'entity_attr_name': 'obs', 'entity_column_class': 'obs'}}</t>
         </is>
       </c>
     </row>
